--- a/4996_Cuenca_Mantaro/_raw_reportes_xlsx/IDConfig_668_completo.xlsx
+++ b/4996_Cuenca_Mantaro/_raw_reportes_xlsx/IDConfig_668_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R71293344c30e406c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R3e8285b5c5ef45b6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,156 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    100.7500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     91.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    114.7500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.0900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.0100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.7300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.0900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.8200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>13/08/2026</x:t>
         </x:is>
       </x:c>

--- a/4996_Cuenca_Mantaro/_raw_reportes_xlsx/IDConfig_668_completo.xlsx
+++ b/4996_Cuenca_Mantaro/_raw_reportes_xlsx/IDConfig_668_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R3e8285b5c5ef45b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R95f39c6da91c4385"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,696 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     81.6500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     96.7100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     97.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     99.8600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     89.2500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    100.3600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     97.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    101.0300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     94.2100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     98.7400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    100.8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    102.0600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     96.7200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    102.0600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     95.5400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.0200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.7900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    114.5500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.7200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.8600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    120.0300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.0200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    114.7600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.7100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    114.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    115.6500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    115.7500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    113.8700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     99.8300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.5800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    113.1600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.1600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    113.7200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.4600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    115.6100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.5600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
